--- a/DataDog Training - 26MMS1005.xlsx
+++ b/DataDog Training - 26MMS1005.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\datadog-teksystems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F8119-74FB-4480-BC87-55B118CFF51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9070D0-15E6-422F-A570-EB17DA4F1FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4C0B1FD6-115A-4E97-B873-2476958F6BA2}"/>
   </bookViews>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
   <si>
     <t xml:space="preserve"> Name</t>
   </si>
@@ -169,6 +167,81 @@
   </si>
   <si>
     <t>Sl. No.</t>
+  </si>
+  <si>
+    <t>100.24.50.11</t>
+  </si>
+  <si>
+    <t>35.153.177.143</t>
+  </si>
+  <si>
+    <t>3.93.0.116</t>
+  </si>
+  <si>
+    <t>3.89.149.69</t>
+  </si>
+  <si>
+    <t>52.90.73.236</t>
+  </si>
+  <si>
+    <t>34.207.225.253</t>
+  </si>
+  <si>
+    <t>3.86.55.233</t>
+  </si>
+  <si>
+    <t>3.84.67.152</t>
+  </si>
+  <si>
+    <t>IP Address</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>ubuntu</t>
+  </si>
+  <si>
+    <t>3.144.14.80</t>
+  </si>
+  <si>
+    <t>18.117.188.11</t>
+  </si>
+  <si>
+    <t>3.15.15.204</t>
+  </si>
+  <si>
+    <t>3.133.113.133</t>
+  </si>
+  <si>
+    <t>18.188.57.156</t>
+  </si>
+  <si>
+    <t>3.145.204.201</t>
+  </si>
+  <si>
+    <t>18.224.67.200</t>
+  </si>
+  <si>
+    <t>18.219.232.94</t>
+  </si>
+  <si>
+    <t>Key Name</t>
+  </si>
+  <si>
+    <t>dd_teksystem_us_east.pem</t>
+  </si>
+  <si>
+    <t>dd_teksystems_us_ohio.pem</t>
+  </si>
+  <si>
+    <t>54.67.130.207</t>
+  </si>
+  <si>
+    <t>18.144.17.229</t>
+  </si>
+  <si>
+    <t>dd_teksystems_us_california</t>
   </si>
 </sst>
 </file>
@@ -238,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -248,6 +321,10 @@
     </xf>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1163,15 +1240,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3A03D4-77D2-4E9B-9288-9962972E6660}">
-  <dimension ref="A2:C22"/>
+  <dimension ref="A2:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1181,8 +1263,17 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1192,8 +1283,17 @@
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1203,8 +1303,17 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1214,8 +1323,17 @@
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1225,8 +1343,17 @@
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1236,8 +1363,17 @@
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1247,8 +1383,17 @@
       <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1258,8 +1403,17 @@
       <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1269,8 +1423,17 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1280,8 +1443,17 @@
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1291,8 +1463,17 @@
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1302,8 +1483,17 @@
       <c r="C13" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1313,8 +1503,17 @@
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1324,8 +1523,17 @@
       <c r="C15" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1335,8 +1543,17 @@
       <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1346,8 +1563,17 @@
       <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1357,8 +1583,17 @@
       <c r="C18" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1368,8 +1603,17 @@
       <c r="C19" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1379,8 +1623,17 @@
       <c r="C20" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1390,8 +1643,11 @@
       <c r="C21" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1401,6 +1657,9 @@
       <c r="C22" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/DataDog Training - 26MMS1005.xlsx
+++ b/DataDog Training - 26MMS1005.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\datadog-teksystems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9070D0-15E6-422F-A570-EB17DA4F1FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFC063F-25A1-4076-8DB1-7F5F76DD7DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4C0B1FD6-115A-4E97-B873-2476958F6BA2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="73">
   <si>
     <t xml:space="preserve"> Name</t>
   </si>
@@ -242,6 +242,21 @@
   </si>
   <si>
     <t>dd_teksystems_us_california</t>
+  </si>
+  <si>
+    <t>18.237.48.98</t>
+  </si>
+  <si>
+    <t>35.90.147.251</t>
+  </si>
+  <si>
+    <t>18.237.121.159</t>
+  </si>
+  <si>
+    <t>44.255.89.135</t>
+  </si>
+  <si>
+    <t>dd_teksystem_us_oregon</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3A03D4-77D2-4E9B-9288-9962972E6660}">
-  <dimension ref="A2:F22"/>
+  <dimension ref="A2:J24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
@@ -1251,6 +1266,8 @@
     <col min="6" max="6" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1553,7 +1570,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1573,7 +1590,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1593,7 +1610,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1613,7 +1630,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1633,7 +1650,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1643,11 +1660,17 @@
       <c r="C21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1657,9 +1680,28 @@
       <c r="C22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
